--- a/trichome measurements.xlsx
+++ b/trichome measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C08BE3-A13A-4F32-8D8B-0623C5EC1D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C582FA6-9FD3-481D-97E1-7CBFFDD0510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2CAEA778-B7A5-4518-A3DF-CB170EC960D9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
   <si>
     <t>mthf circle trichome</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>ithf_trichome</t>
+  </si>
+  <si>
+    <t>avg length of branches</t>
   </si>
 </sst>
 </file>
@@ -440,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21B7ACB-A879-4126-944D-F29E8C755DBB}">
-  <dimension ref="B2:L14"/>
+  <dimension ref="B2:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -540,6 +543,13 @@
       <c r="I6">
         <v>47.078000000000003</v>
       </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <f>(L3+L4+L5)/3</f>
+        <v>25.235333333333333</v>
+      </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H7">
@@ -549,6 +559,15 @@
         <v>78.480999999999995</v>
       </c>
     </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <f>(I3+I4+I5+I6+I7)/5</f>
+        <v>49.768599999999999</v>
+      </c>
+    </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>6</v>
@@ -623,6 +642,15 @@
       </c>
       <c r="L14">
         <v>35.009</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <f>(L11+L12+L13+L14)/4</f>
+        <v>43.127250000000004</v>
       </c>
     </row>
   </sheetData>
